--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_individual_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_individual_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.008472363430969096</v>
       </c>
       <c r="C2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>31638587</v>
+        <v>4155243</v>
       </c>
       <c r="L2" t="n">
-        <v>18014629</v>
+        <v>2047583</v>
       </c>
       <c r="M2" t="n">
-        <v>4416033</v>
+        <v>453682</v>
       </c>
       <c r="N2" t="n">
-        <v>188853</v>
+        <v>10958</v>
       </c>
       <c r="O2" t="n">
-        <v>2614301</v>
+        <v>263230</v>
       </c>
       <c r="P2" t="n">
-        <v>1036616</v>
+        <v>105718</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999042153358459</v>
+        <v>0.9998573064804077</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8868290781974792</v>
+        <v>0.7978972196578979</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7783058285713196</v>
+        <v>0.629580557346344</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7212210893630981</v>
+        <v>0.5258117914199829</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3425774276256561</v>
+        <v>0.1076392605900764</v>
       </c>
       <c r="V2" t="n">
-        <v>0.771634578704834</v>
+        <v>0.5929217934608459</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8442763686180115</v>
+        <v>0.7186664938926697</v>
       </c>
       <c r="X2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44190846</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="AG2" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AH2" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AI2" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563413858413696</v>
+        <v>0.9555707573890686</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113937020301819</v>
+        <v>0.9118538498878479</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582093119621277</v>
+        <v>0.8584820032119751</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620789766311646</v>
+        <v>0.6613538861274719</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020217657089233</v>
+        <v>0.9020804166793823</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002030617636925397</v>
       </c>
       <c r="C3" t="n">
-        <v>2456</v>
+        <v>556</v>
       </c>
       <c r="D3" t="n">
-        <v>31638587</v>
+        <v>4155243</v>
       </c>
       <c r="E3" t="n">
-        <v>3433168</v>
+        <v>815541</v>
       </c>
       <c r="F3" t="n">
-        <v>67107</v>
+        <v>24566</v>
       </c>
       <c r="G3" t="n">
-        <v>5951</v>
+        <v>1657</v>
       </c>
       <c r="H3" t="n">
-        <v>3842</v>
+        <v>1497</v>
       </c>
       <c r="I3" t="n">
-        <v>178</v>
+        <v>81</v>
       </c>
       <c r="J3" t="n">
-        <v>70112121</v>
+        <v>10015721</v>
       </c>
       <c r="K3" t="n">
-        <v>75118415</v>
+        <v>10277960</v>
       </c>
       <c r="L3" t="n">
-        <v>86287924</v>
+        <v>11837367</v>
       </c>
       <c r="M3" t="n">
-        <v>106067360</v>
+        <v>14983911</v>
       </c>
       <c r="N3" t="n">
-        <v>113320327</v>
+        <v>16149291</v>
       </c>
       <c r="O3" t="n">
-        <v>109967250</v>
+        <v>15638434</v>
       </c>
       <c r="P3" t="n">
-        <v>112762468</v>
+        <v>16094708</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9000690579414368</v>
+        <v>0.8311914205551147</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7870790958404541</v>
+        <v>0.6228353381156921</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6759705543518066</v>
+        <v>0.4844188690185547</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3024285137653351</v>
+        <v>0.1224850192666054</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7330678701400757</v>
+        <v>0.5156903266906738</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7658599615097046</v>
+        <v>0.5463265180587769</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33659447</v>
+        <v>4787035</v>
       </c>
       <c r="Z3" t="n">
-        <v>1384204</v>
+        <v>196812</v>
       </c>
       <c r="AA3" t="n">
-        <v>59560</v>
+        <v>8425</v>
       </c>
       <c r="AB3" t="n">
-        <v>47621</v>
+        <v>6828</v>
       </c>
       <c r="AC3" t="n">
-        <v>247</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70116354</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>77619300</v>
+        <v>11107886</v>
       </c>
       <c r="AG3" t="n">
-        <v>89394449</v>
+        <v>12753027</v>
       </c>
       <c r="AH3" t="n">
-        <v>106848837</v>
+        <v>15260727</v>
       </c>
       <c r="AI3" t="n">
-        <v>113471912</v>
+        <v>16209880</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110391725</v>
+        <v>15769225</v>
       </c>
       <c r="AK3" t="n">
-        <v>112860888</v>
+        <v>16122838</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575594067573547</v>
+        <v>0.9575715065002441</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099474549293518</v>
+        <v>0.9095625281333923</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574531674385071</v>
+        <v>0.8570923805236816</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6615032553672791</v>
+        <v>0.6604667901992798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015399217605591</v>
+        <v>0.9011915326118469</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03203040203446905</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3790184</v>
+        <v>981748</v>
       </c>
       <c r="E4" t="n">
-        <v>18014629</v>
+        <v>2047583</v>
       </c>
       <c r="F4" t="n">
-        <v>964327</v>
+        <v>220488</v>
       </c>
       <c r="G4" t="n">
-        <v>37395</v>
+        <v>11545</v>
       </c>
       <c r="H4" t="n">
-        <v>75228</v>
+        <v>23928</v>
       </c>
       <c r="I4" t="n">
-        <v>6179</v>
+        <v>2221</v>
       </c>
       <c r="J4" t="n">
-        <v>4233</v>
+        <v>901</v>
       </c>
       <c r="K4" t="n">
-        <v>4037496</v>
+        <v>1052499</v>
       </c>
       <c r="L4" t="n">
-        <v>5131323</v>
+        <v>1204714</v>
       </c>
       <c r="M4" t="n">
-        <v>1706962</v>
+        <v>409140</v>
       </c>
       <c r="N4" t="n">
-        <v>362418</v>
+        <v>90845</v>
       </c>
       <c r="O4" t="n">
-        <v>773703</v>
+        <v>180724</v>
       </c>
       <c r="P4" t="n">
-        <v>191200</v>
+        <v>41385</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999521374702454</v>
+        <v>0.9999286532402039</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8934000134468079</v>
+        <v>0.8142040967941284</v>
       </c>
       <c r="S4" t="n">
-        <v>0.782667875289917</v>
+        <v>0.6261897683143616</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6978630423545837</v>
+        <v>0.5042673349380493</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3212534189224243</v>
+        <v>0.1145832762122154</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7518569827079773</v>
+        <v>0.5516158938407898</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8031586408615112</v>
+        <v>0.6207569241523743</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1434717</v>
+        <v>207948</v>
       </c>
       <c r="Z4" t="n">
-        <v>20826834</v>
+        <v>2990204</v>
       </c>
       <c r="AA4" t="n">
-        <v>579437</v>
+        <v>82633</v>
       </c>
       <c r="AB4" t="n">
-        <v>38501</v>
+        <v>5536</v>
       </c>
       <c r="AC4" t="n">
-        <v>7988</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1536611</v>
+        <v>222573</v>
       </c>
       <c r="AG4" t="n">
-        <v>2024798</v>
+        <v>289054</v>
       </c>
       <c r="AH4" t="n">
-        <v>925485</v>
+        <v>132324</v>
       </c>
       <c r="AI4" t="n">
-        <v>210833</v>
+        <v>30256</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349228</v>
+        <v>49933</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569499492645264</v>
+        <v>0.9565700888633728</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106699824333191</v>
+        <v>0.9107067584991455</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578310608863831</v>
+        <v>0.8577865958213806</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617910265922546</v>
+        <v>0.6609100103378296</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017807841300964</v>
+        <v>0.9016357064247131</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1214</v>
+        <v>180</v>
       </c>
       <c r="D5" t="n">
-        <v>163241</v>
+        <v>50149</v>
       </c>
       <c r="E5" t="n">
-        <v>1439878</v>
+        <v>319318</v>
       </c>
       <c r="F5" t="n">
-        <v>4416033</v>
+        <v>453682</v>
       </c>
       <c r="G5" t="n">
-        <v>127076</v>
+        <v>28321</v>
       </c>
       <c r="H5" t="n">
-        <v>354408</v>
+        <v>75419</v>
       </c>
       <c r="I5" t="n">
-        <v>31028</v>
+        <v>9480</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3512702</v>
+        <v>843898</v>
       </c>
       <c r="L5" t="n">
-        <v>4873324</v>
+        <v>1239936</v>
       </c>
       <c r="M5" t="n">
-        <v>2116845</v>
+        <v>482867</v>
       </c>
       <c r="N5" t="n">
-        <v>435602</v>
+        <v>78506</v>
       </c>
       <c r="O5" t="n">
-        <v>951946</v>
+        <v>247212</v>
       </c>
       <c r="P5" t="n">
-        <v>316916</v>
+        <v>87789</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999629855155945</v>
+        <v>0.999944806098938</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9339481592178345</v>
+        <v>0.8838675022125244</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9124757647514343</v>
+        <v>0.8502933382987976</v>
       </c>
       <c r="T5" t="n">
-        <v>0.966547966003418</v>
+        <v>0.9453748464584351</v>
       </c>
       <c r="U5" t="n">
-        <v>0.993018627166748</v>
+        <v>0.9896292090415955</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9849033951759338</v>
+        <v>0.9737938642501831</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9955548048019409</v>
+        <v>0.992089569568634</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56186</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>596891</v>
+        <v>86001</v>
       </c>
       <c r="AA5" t="n">
-        <v>5601637</v>
+        <v>802709</v>
       </c>
       <c r="AB5" t="n">
-        <v>69704</v>
+        <v>9990</v>
       </c>
       <c r="AC5" t="n">
-        <v>204029</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1491842</v>
+        <v>212106</v>
       </c>
       <c r="AG5" t="n">
-        <v>2061119</v>
+        <v>297315</v>
       </c>
       <c r="AH5" t="n">
-        <v>931241</v>
+        <v>133840</v>
       </c>
       <c r="AI5" t="n">
-        <v>211376</v>
+        <v>30376</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351133</v>
+        <v>50436</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735060334205627</v>
+        <v>0.9733809232711792</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642549753189087</v>
+        <v>0.9640916585922241</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837567210197449</v>
+        <v>0.9837005138397217</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963063597679138</v>
+        <v>0.9962869882583618</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938730001449585</v>
+        <v>0.9938535690307617</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983745217323303</v>
+        <v>0.9983724355697632</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>250</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
-        <v>78860</v>
+        <v>17515</v>
       </c>
       <c r="E6" t="n">
-        <v>130306</v>
+        <v>21419</v>
       </c>
       <c r="F6" t="n">
-        <v>149602</v>
+        <v>27888</v>
       </c>
       <c r="G6" t="n">
-        <v>188853</v>
+        <v>10958</v>
       </c>
       <c r="H6" t="n">
-        <v>70775</v>
+        <v>10403</v>
       </c>
       <c r="I6" t="n">
-        <v>5809</v>
+        <v>1242</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45337</v>
+        <v>6558</v>
       </c>
       <c r="Z6" t="n">
-        <v>37466</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>76329</v>
+        <v>10994</v>
       </c>
       <c r="AB6" t="n">
-        <v>413079</v>
+        <v>59088</v>
       </c>
       <c r="AC6" t="n">
-        <v>48877</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>4920</v>
+        <v>3002</v>
       </c>
       <c r="E7" t="n">
-        <v>119878</v>
+        <v>44690</v>
       </c>
       <c r="F7" t="n">
-        <v>500612</v>
+        <v>126645</v>
       </c>
       <c r="G7" t="n">
-        <v>178433</v>
+        <v>44471</v>
       </c>
       <c r="H7" t="n">
-        <v>2614301</v>
+        <v>263230</v>
       </c>
       <c r="I7" t="n">
-        <v>148006</v>
+        <v>28361</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>5670</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207844</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53148</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215114</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>85</v>
       </c>
       <c r="E8" t="n">
-        <v>8093</v>
+        <v>3746</v>
       </c>
       <c r="F8" t="n">
-        <v>25314</v>
+        <v>9553</v>
       </c>
       <c r="G8" t="n">
-        <v>13563</v>
+        <v>4851</v>
       </c>
       <c r="H8" t="n">
-        <v>269450</v>
+        <v>69477</v>
       </c>
       <c r="I8" t="n">
-        <v>1036616</v>
+        <v>105718</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
